--- a/CoordonnePoints.xlsx
+++ b/CoordonnePoints.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\images_scierie\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeanlouis\SiteMoulin\moulindunoiret\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DFCB9B-2FDA-4E44-93FB-26B4E290525B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31507CC1-69C7-4212-9044-EF5D7FB7EC44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-78" yWindow="0" windowWidth="11676" windowHeight="12318" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="34">
   <si>
     <t>num</t>
   </si>
@@ -61,24 +61,9 @@
     <t>5_ScieRennepont.jpg</t>
   </si>
   <si>
-    <t>6_PostPilotScie.jpg</t>
-  </si>
-  <si>
-    <t>7_TapisRoulant.jpg</t>
-  </si>
-  <si>
-    <t>8_LaPropio.jpg</t>
-  </si>
-  <si>
-    <t>9_TapisRoulant.jpg</t>
-  </si>
-  <si>
     <t>10_ScieADelignier.jpg</t>
   </si>
   <si>
-    <t>11_DosssesPapetterie.jpg</t>
-  </si>
-  <si>
     <t>14_GrueScieBatt.jpg</t>
   </si>
   <si>
@@ -91,9 +76,6 @@
     <t>19_TransfoSW.jpg</t>
   </si>
   <si>
-    <t>20_SW.jpg</t>
-  </si>
-  <si>
     <t>21_HanguarCamions.jpg</t>
   </si>
   <si>
@@ -109,32 +91,71 @@
     <t>&lt;---taille image en pixel</t>
   </si>
   <si>
-    <t>x pixel</t>
-  </si>
-  <si>
-    <t>y pixel</t>
-  </si>
-  <si>
     <t>&lt;---x0, y0</t>
   </si>
   <si>
-    <t>277,590</t>
-  </si>
-  <si>
     <t>18_QuaiChargement.jpg</t>
+  </si>
+  <si>
+    <t>x %</t>
+  </si>
+  <si>
+    <t>y%</t>
+  </si>
+  <si>
+    <t>&lt;MapButton x={</t>
+  </si>
+  <si>
+    <t>} y={</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "onClick={setSelectedImage}/&gt;</t>
+  </si>
+  <si>
+    <t>} imagePath="../images_H3/</t>
+  </si>
+  <si>
+    <t>6_JeanLeScieur.jpg</t>
+  </si>
+  <si>
+    <t>7_PostPilotScie.jpg</t>
+  </si>
+  <si>
+    <t>8_TapisRoulant.jpg</t>
+  </si>
+  <si>
+    <t>9_LaPropio.jpg</t>
+  </si>
+  <si>
+    <t>1_NW.jpg</t>
+  </si>
+  <si>
+    <t>12_GrandePiece.jpg</t>
+  </si>
+  <si>
+    <t>20_W.jpg</t>
+  </si>
+  <si>
+    <t>11_DossesPapetterie.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="4"/>
+      <color rgb="FF808080"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="6">
@@ -181,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -203,6 +224,10 @@
     <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,14 +532,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="4" max="7" width="10.9453125" style="2"/>
     <col min="8" max="8" width="21.20703125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="13.20703125" customWidth="1"/>
+    <col min="11" max="11" width="7.20703125" customWidth="1"/>
+    <col min="12" max="12" width="4.3125" customWidth="1"/>
+    <col min="13" max="13" width="5.62890625" customWidth="1"/>
+    <col min="15" max="15" width="11.83984375" customWidth="1"/>
+    <col min="16" max="16" width="19.7890625" customWidth="1"/>
+    <col min="18" max="18" width="16.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="C1" t="s">
         <v>3</v>
       </c>
@@ -531,10 +563,10 @@
         <v>620</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="F2" s="6">
         <v>28</v>
       </c>
@@ -542,15 +574,16 @@
         <v>-23</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="5"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J3" s="9"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -561,26 +594,73 @@
         <v>2</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.8</v>
+      </c>
+      <c r="D5" s="3">
+        <f>B5/$D$1</f>
+        <v>0.32051282051282054</v>
+      </c>
+      <c r="E5" s="3">
+        <f>1-C5/$E$1</f>
+        <v>0.57664233576642343</v>
+      </c>
+      <c r="F5" s="8">
+        <f>D5*$F$1+$F$2</f>
+        <v>255.56410256410257</v>
+      </c>
+      <c r="G5" s="8">
+        <f>E5*$G$1+$G$2</f>
+        <v>334.51824817518252</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="10">
+        <f>D5*100</f>
+        <v>32.051282051282051</v>
+      </c>
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="10">
+        <f>E5*100</f>
+        <v>57.664233576642346</v>
+      </c>
+      <c r="N5" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" t="str">
+        <f>H5</f>
+        <v>1_NW.jpg</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>2</v>
       </c>
@@ -609,8 +689,32 @@
       <c r="H6" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="10">
+        <f>D6*100</f>
+        <v>66.666666666666671</v>
+      </c>
+      <c r="L6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="10">
+        <f>E6*100</f>
+        <v>2.1897810218978075</v>
+      </c>
+      <c r="N6" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" t="str">
+        <f>H6</f>
+        <v>2_StocBilles.jpg</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>3</v>
       </c>
@@ -621,29 +725,50 @@
         <v>0.2</v>
       </c>
       <c r="D7" s="3">
-        <f t="shared" ref="D7:D26" si="0">B7/$D$1</f>
+        <f t="shared" ref="D7:D24" si="0">B7/$D$1</f>
         <v>0.35256410256410259</v>
       </c>
       <c r="E7" s="3">
-        <f t="shared" ref="E7:E26" si="1">1-C7/$E$1</f>
+        <f t="shared" ref="E7:E24" si="1">1-C7/$E$1</f>
         <v>0.98540145985401462</v>
       </c>
       <c r="F7" s="8">
-        <f t="shared" ref="F7:F26" si="2">D7*$F$1+$F$2</f>
+        <f t="shared" ref="F7:F24" si="2">D7*$F$1+$F$2</f>
         <v>278.32051282051282</v>
       </c>
       <c r="G7" s="8">
-        <f t="shared" ref="G7:G27" si="3">E7*$G$1+$G$2</f>
+        <f t="shared" ref="G7:G24" si="3">E7*$G$1+$G$2</f>
         <v>587.94890510948903</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="10">
+        <f t="shared" ref="K7:K24" si="4">D7*100</f>
+        <v>35.256410256410255</v>
+      </c>
+      <c r="L7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" s="10">
+        <f t="shared" ref="M7:M24" si="5">E7*100</f>
+        <v>98.540145985401466</v>
+      </c>
+      <c r="N7" t="s">
+        <v>25</v>
+      </c>
+      <c r="P7" t="str">
+        <f t="shared" ref="P7:P24" si="6">H7</f>
+        <v>3_StocBilles.jpg</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>4</v>
       </c>
@@ -672,8 +797,32 @@
       <c r="H8" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="10">
+        <f t="shared" si="4"/>
+        <v>83.333333333333343</v>
+      </c>
+      <c r="L8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" s="10">
+        <f t="shared" si="5"/>
+        <v>35.036496350364956</v>
+      </c>
+      <c r="N8" t="s">
+        <v>25</v>
+      </c>
+      <c r="P8" t="str">
+        <f t="shared" si="6"/>
+        <v>4_Billonnage.jpg</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>5</v>
       </c>
@@ -684,11 +833,11 @@
         <v>7.15</v>
       </c>
       <c r="D9" s="3">
-        <f t="shared" ref="D9" si="4">B9/$D$1</f>
+        <f t="shared" ref="D9" si="7">B9/$D$1</f>
         <v>0.80128205128205132</v>
       </c>
       <c r="E9" s="3">
-        <f t="shared" ref="E9" si="5">1-C9/$E$1</f>
+        <f t="shared" ref="E9" si="8">1-C9/$E$1</f>
         <v>0.47810218978102181</v>
       </c>
       <c r="F9" s="8">
@@ -702,8 +851,32 @@
       <c r="H9" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="10">
+        <f t="shared" si="4"/>
+        <v>80.128205128205138</v>
+      </c>
+      <c r="L9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" s="10">
+        <f t="shared" si="5"/>
+        <v>47.810218978102185</v>
+      </c>
+      <c r="N9" t="s">
+        <v>25</v>
+      </c>
+      <c r="P9" t="str">
+        <f t="shared" si="6"/>
+        <v>5_ScieRennepont.jpg</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>6</v>
       </c>
@@ -711,158 +884,317 @@
         <v>13</v>
       </c>
       <c r="C10">
+        <v>7.17</v>
+      </c>
+      <c r="D10" s="3">
+        <f t="shared" ref="D10" si="9">B10/$D$1</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" ref="E10" si="10">1-C10/$E$1</f>
+        <v>0.47664233576642334</v>
+      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="10">
+        <f t="shared" ref="K10" si="11">D10*100</f>
+        <v>83.333333333333343</v>
+      </c>
+      <c r="L10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="10">
+        <f t="shared" ref="M10" si="12">E10*100</f>
+        <v>47.664233576642332</v>
+      </c>
+      <c r="N10" t="s">
+        <v>25</v>
+      </c>
+      <c r="P10" t="str">
+        <f t="shared" ref="P10" si="13">H10</f>
+        <v>6_JeanLeScieur.jpg</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>13.5</v>
+      </c>
+      <c r="C11">
         <v>7.2</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D11" s="3">
         <f t="shared" si="0"/>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="E10" s="3">
+        <v>0.86538461538461542</v>
+      </c>
+      <c r="E11" s="3">
         <f t="shared" si="1"/>
         <v>0.47445255474452552</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F11" s="8">
         <f t="shared" si="2"/>
-        <v>619.66666666666674</v>
-      </c>
-      <c r="G10" s="8">
+        <v>642.42307692307691</v>
+      </c>
+      <c r="G11" s="8">
         <f t="shared" si="3"/>
         <v>271.16058394160581</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="10">
+        <f t="shared" si="4"/>
+        <v>86.538461538461547</v>
+      </c>
+      <c r="L11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="10">
+        <f t="shared" si="5"/>
+        <v>47.445255474452551</v>
+      </c>
+      <c r="N11" t="s">
+        <v>25</v>
+      </c>
+      <c r="P11" t="str">
+        <f t="shared" si="6"/>
+        <v>7_PostPilotScie.jpg</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11">
+      <c r="B12">
+        <v>11.8</v>
+      </c>
+      <c r="C12">
         <v>7</v>
       </c>
-      <c r="B11">
-        <v>11.8</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>0.7564102564102565</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E12" s="3">
         <f t="shared" si="1"/>
         <v>0.48905109489051091</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F12" s="8">
         <f t="shared" si="2"/>
         <v>565.0512820512821</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G12" s="8">
         <f t="shared" si="3"/>
         <v>280.21167883211677</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="10">
+        <f t="shared" si="4"/>
+        <v>75.641025641025649</v>
+      </c>
+      <c r="L12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" s="10">
+        <f t="shared" si="5"/>
+        <v>48.905109489051092</v>
+      </c>
+      <c r="N12" t="s">
+        <v>25</v>
+      </c>
+      <c r="P12" t="str">
+        <f t="shared" si="6"/>
+        <v>8_TapisRoulant.jpg</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12">
-        <v>8</v>
-      </c>
-      <c r="B12">
+      <c r="B13">
         <v>9.4</v>
       </c>
-      <c r="C12">
+      <c r="C13">
         <v>7.2</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>0.60256410256410264</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E13" s="3">
         <f t="shared" si="1"/>
         <v>0.47445255474452552</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F13" s="8">
         <f t="shared" si="2"/>
         <v>455.82051282051287</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G13" s="8">
         <f t="shared" si="3"/>
         <v>271.16058394160581</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="10">
+        <f t="shared" si="4"/>
+        <v>60.256410256410263</v>
+      </c>
+      <c r="L13" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" s="10">
+        <f t="shared" si="5"/>
+        <v>47.445255474452551</v>
+      </c>
+      <c r="N13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P13" t="str">
+        <f t="shared" si="6"/>
+        <v>9_LaPropio.jpg</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13">
-        <v>9</v>
-      </c>
-      <c r="B13">
+      <c r="B14">
         <v>10.4</v>
       </c>
-      <c r="C13">
+      <c r="C14">
         <v>6.8</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>0.66666666666666674</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E14" s="3">
         <f t="shared" si="1"/>
         <v>0.50364963503649629</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F14" s="8">
         <f t="shared" si="2"/>
         <v>501.33333333333337</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G14" s="8">
         <f t="shared" si="3"/>
         <v>289.26277372262768</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="10">
+        <f t="shared" si="4"/>
+        <v>66.666666666666671</v>
+      </c>
+      <c r="L14" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14" s="10">
+        <f t="shared" si="5"/>
+        <v>50.364963503649626</v>
+      </c>
+      <c r="N14" t="s">
+        <v>25</v>
+      </c>
+      <c r="P14" t="str">
+        <f t="shared" si="6"/>
+        <v>10_ScieADelignier.jpg</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14">
-        <v>10</v>
-      </c>
-      <c r="B14">
+      <c r="B15">
         <v>8.8000000000000007</v>
       </c>
-      <c r="C14">
+      <c r="C15">
         <v>6.4</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D15" s="3">
         <f t="shared" si="0"/>
         <v>0.56410256410256421</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E15" s="3">
         <f t="shared" si="1"/>
         <v>0.53284671532846706</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F15" s="8">
         <f t="shared" si="2"/>
         <v>428.51282051282061</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G15" s="8">
         <f t="shared" si="3"/>
         <v>307.36496350364956</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15">
-        <v>11</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="H15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J15" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="10">
+        <f t="shared" si="4"/>
+        <v>56.410256410256423</v>
+      </c>
+      <c r="L15" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" s="10">
+        <f t="shared" si="5"/>
+        <v>53.284671532846708</v>
+      </c>
+      <c r="N15" t="s">
+        <v>25</v>
+      </c>
+      <c r="P15" t="str">
+        <f>H15</f>
+        <v>11_DossesPapetterie.jpg</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>12</v>
       </c>
@@ -889,294 +1221,506 @@
         <v>325.4671532846715</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>31</v>
+      </c>
+      <c r="J16" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="10">
+        <f t="shared" si="4"/>
+        <v>42.948717948717949</v>
+      </c>
+      <c r="L16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M16" s="10">
+        <f t="shared" si="5"/>
+        <v>56.20437956204379</v>
+      </c>
+      <c r="N16" t="s">
+        <v>25</v>
+      </c>
+      <c r="P16" t="str">
+        <f t="shared" si="6"/>
+        <v>12_GrandePiece.jpg</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
-        <v>13</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>14</v>
+      </c>
+      <c r="B17">
+        <v>6.8</v>
+      </c>
+      <c r="C17">
+        <v>6.8</v>
+      </c>
+      <c r="D17" s="3">
+        <f t="shared" si="0"/>
+        <v>0.4358974358974359</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="1"/>
+        <v>0.50364963503649629</v>
+      </c>
+      <c r="F17" s="8">
+        <f t="shared" si="2"/>
+        <v>337.4871794871795</v>
+      </c>
+      <c r="G17" s="8">
+        <f t="shared" si="3"/>
+        <v>289.26277372262768</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="10">
+        <f t="shared" si="4"/>
+        <v>43.589743589743591</v>
+      </c>
+      <c r="L17" t="s">
+        <v>23</v>
+      </c>
+      <c r="M17" s="10">
+        <f t="shared" si="5"/>
+        <v>50.364963503649626</v>
+      </c>
+      <c r="N17" t="s">
+        <v>25</v>
+      </c>
+      <c r="P17" t="str">
+        <f t="shared" si="6"/>
+        <v>14_GrueScieBatt.jpg</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B18">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="C18">
-        <v>6.8</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
-        <v>0.4358974358974359</v>
+        <v>0.48076923076923078</v>
       </c>
       <c r="E18" s="3">
         <f t="shared" si="1"/>
-        <v>0.50364963503649629</v>
+        <v>0.35766423357664223</v>
       </c>
       <c r="F18" s="8">
         <f t="shared" si="2"/>
-        <v>337.4871794871795</v>
+        <v>369.34615384615387</v>
       </c>
       <c r="G18" s="8">
         <f t="shared" si="3"/>
-        <v>289.26277372262768</v>
+        <v>198.75182481751818</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>10</v>
+      </c>
+      <c r="J18" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="10">
+        <f t="shared" si="4"/>
+        <v>48.07692307692308</v>
+      </c>
+      <c r="L18" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18" s="10">
+        <f t="shared" si="5"/>
+        <v>35.766423357664223</v>
+      </c>
+      <c r="N18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P18" t="str">
+        <f t="shared" si="6"/>
+        <v>16_QuaiChargement.jpg</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
-        <v>15</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>7.4</v>
+      </c>
+      <c r="C19">
+        <v>10.5</v>
+      </c>
+      <c r="D19" s="3">
+        <f>B19/$D$1</f>
+        <v>0.47435897435897439</v>
+      </c>
+      <c r="E19" s="3">
+        <f>1-C19/$E$1</f>
+        <v>0.23357664233576636</v>
+      </c>
+      <c r="F19" s="8">
+        <f t="shared" si="2"/>
+        <v>364.79487179487182</v>
+      </c>
+      <c r="G19" s="8">
+        <f t="shared" si="3"/>
+        <v>121.81751824817513</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J19" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" s="10">
+        <f t="shared" si="4"/>
+        <v>47.435897435897438</v>
+      </c>
+      <c r="L19" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" s="10">
+        <f t="shared" si="5"/>
+        <v>23.357664233576635</v>
+      </c>
+      <c r="N19" t="s">
+        <v>25</v>
+      </c>
+      <c r="P19" t="str">
+        <f t="shared" si="6"/>
+        <v>17_QuaiChargement.jpg</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B20">
-        <v>7.5</v>
+        <v>15.2</v>
       </c>
       <c r="C20">
-        <v>8.8000000000000007</v>
+        <v>12.6</v>
       </c>
       <c r="D20" s="3">
+        <f>B20/$D$1</f>
+        <v>0.97435897435897434</v>
+      </c>
+      <c r="E20" s="3">
+        <f>1-C20/$E$1</f>
+        <v>8.0291970802919721E-2</v>
+      </c>
+      <c r="F20" s="8">
+        <f t="shared" ref="F20" si="14">D20*$F$1+$F$2</f>
+        <v>719.79487179487182</v>
+      </c>
+      <c r="G20" s="8">
+        <f>E20*$G$1+$G$2</f>
+        <v>26.781021897810227</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" s="10">
+        <f t="shared" si="4"/>
+        <v>97.435897435897431</v>
+      </c>
+      <c r="L20" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" s="10">
+        <f t="shared" si="5"/>
+        <v>8.0291970802919721</v>
+      </c>
+      <c r="N20" t="s">
+        <v>25</v>
+      </c>
+      <c r="P20" t="str">
+        <f t="shared" si="6"/>
+        <v>18_QuaiChargement.jpg</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>12.4</v>
+      </c>
+      <c r="C21">
+        <v>4.8</v>
+      </c>
+      <c r="D21" s="3">
         <f t="shared" si="0"/>
-        <v>0.48076923076923078</v>
-      </c>
-      <c r="E20" s="3">
+        <v>0.79487179487179493</v>
+      </c>
+      <c r="E21" s="3">
         <f t="shared" si="1"/>
-        <v>0.35766423357664223</v>
-      </c>
-      <c r="F20" s="8">
-        <f t="shared" si="2"/>
-        <v>369.34615384615387</v>
-      </c>
-      <c r="G20" s="8">
-        <f t="shared" si="3"/>
-        <v>198.75182481751818</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21">
-        <v>17</v>
-      </c>
-      <c r="B21">
-        <v>7.4</v>
-      </c>
-      <c r="C21">
-        <v>10.5</v>
-      </c>
-      <c r="D21" s="3">
-        <f>B21/$D$1</f>
-        <v>0.47435897435897439</v>
-      </c>
-      <c r="E21" s="3">
-        <f>1-C21/$E$1</f>
-        <v>0.23357664233576636</v>
+        <v>0.64963503649635035</v>
       </c>
       <c r="F21" s="8">
         <f t="shared" si="2"/>
-        <v>364.79487179487182</v>
+        <v>592.35897435897436</v>
       </c>
       <c r="G21" s="8">
         <f t="shared" si="3"/>
-        <v>121.81751824817513</v>
+        <v>379.77372262773724</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>12</v>
+      </c>
+      <c r="J21" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" s="10">
+        <f t="shared" si="4"/>
+        <v>79.487179487179489</v>
+      </c>
+      <c r="L21" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" s="10">
+        <f t="shared" si="5"/>
+        <v>64.96350364963503</v>
+      </c>
+      <c r="N21" t="s">
+        <v>25</v>
+      </c>
+      <c r="P21" t="str">
+        <f t="shared" si="6"/>
+        <v>19_TransfoSW.jpg</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B22">
-        <v>15.2</v>
+        <v>6.2</v>
       </c>
       <c r="C22">
-        <v>12.6</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D22" s="3">
-        <f>B22/$D$1</f>
-        <v>0.97435897435897434</v>
+        <f t="shared" si="0"/>
+        <v>0.39743589743589747</v>
       </c>
       <c r="E22" s="3">
-        <f>1-C22/$E$1</f>
-        <v>8.0291970802919721E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.7007299270072993</v>
       </c>
       <c r="F22" s="8">
-        <f t="shared" ref="F22" si="6">D22*$F$1+$F$2</f>
-        <v>719.79487179487182</v>
+        <f t="shared" si="2"/>
+        <v>310.17948717948718</v>
       </c>
       <c r="G22" s="8">
-        <f>E22*$G$1+$G$2</f>
-        <v>26.781021897810227</v>
+        <f t="shared" si="3"/>
+        <v>411.45255474452557</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>32</v>
+      </c>
+      <c r="J22" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="10">
+        <f t="shared" si="4"/>
+        <v>39.743589743589745</v>
+      </c>
+      <c r="L22" t="s">
+        <v>23</v>
+      </c>
+      <c r="M22" s="10">
+        <f t="shared" si="5"/>
+        <v>70.072992700729927</v>
+      </c>
+      <c r="N22" t="s">
+        <v>25</v>
+      </c>
+      <c r="P22" t="str">
+        <f>H22</f>
+        <v>20_W.jpg</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B23">
-        <v>12.4</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="C23">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
-        <v>0.79487179487179493</v>
+        <v>0.52564102564102566</v>
       </c>
       <c r="E23" s="3">
         <f t="shared" si="1"/>
-        <v>0.64963503649635035</v>
+        <v>0.63503649635036497</v>
       </c>
       <c r="F23" s="8">
         <f t="shared" si="2"/>
-        <v>592.35897435897436</v>
+        <v>401.20512820512823</v>
       </c>
       <c r="G23" s="8">
         <f t="shared" si="3"/>
-        <v>379.77372262773724</v>
+        <v>370.72262773722628</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>13</v>
+      </c>
+      <c r="J23" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" s="10">
+        <f t="shared" si="4"/>
+        <v>52.564102564102569</v>
+      </c>
+      <c r="L23" t="s">
+        <v>23</v>
+      </c>
+      <c r="M23" s="10">
+        <f t="shared" si="5"/>
+        <v>63.503649635036496</v>
+      </c>
+      <c r="N23" t="s">
+        <v>25</v>
+      </c>
+      <c r="P23" t="str">
+        <f t="shared" si="6"/>
+        <v>21_HanguarCamions.jpg</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B24">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="C24">
-        <v>4.0999999999999996</v>
+        <v>8</v>
       </c>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
-        <v>0.39743589743589747</v>
+        <v>0.4358974358974359</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" si="1"/>
-        <v>0.7007299270072993</v>
+        <v>0.41605839416058388</v>
       </c>
       <c r="F24" s="8">
         <f t="shared" si="2"/>
-        <v>310.17948717948718</v>
+        <v>337.4871794871795</v>
       </c>
       <c r="G24" s="8">
         <f t="shared" si="3"/>
-        <v>411.45255474452557</v>
+        <v>234.956204379562</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>14</v>
+      </c>
+      <c r="J24" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" s="10">
+        <f t="shared" si="4"/>
+        <v>43.589743589743591</v>
+      </c>
+      <c r="L24" t="s">
+        <v>23</v>
+      </c>
+      <c r="M24" s="10">
+        <f t="shared" si="5"/>
+        <v>41.605839416058387</v>
+      </c>
+      <c r="N24" t="s">
+        <v>25</v>
+      </c>
+      <c r="P24" t="str">
+        <f t="shared" si="6"/>
+        <v>22_LocalSciure.jpg</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
-        <v>21</v>
-      </c>
-      <c r="B25">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="C25">
-        <v>5</v>
-      </c>
-      <c r="D25" s="3">
-        <f t="shared" si="0"/>
-        <v>0.52564102564102566</v>
-      </c>
-      <c r="E25" s="3">
-        <f t="shared" si="1"/>
-        <v>0.63503649635036497</v>
-      </c>
-      <c r="F25" s="8">
-        <f t="shared" si="2"/>
-        <v>401.20512820512823</v>
-      </c>
-      <c r="G25" s="8">
-        <f t="shared" si="3"/>
-        <v>370.72262773722628</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26">
-        <v>22</v>
-      </c>
-      <c r="B26">
-        <v>6.8</v>
-      </c>
-      <c r="C26">
-        <v>8</v>
-      </c>
-      <c r="D26" s="3">
-        <f t="shared" si="0"/>
-        <v>0.4358974358974359</v>
-      </c>
-      <c r="E26" s="3">
-        <f t="shared" si="1"/>
-        <v>0.41605839416058388</v>
-      </c>
-      <c r="F26" s="8">
-        <f t="shared" si="2"/>
-        <v>337.4871794871795</v>
-      </c>
-      <c r="G26" s="8">
-        <f t="shared" si="3"/>
-        <v>234.956204379562</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D29"/>
       <c r="E29"/>
       <c r="F29"/>
       <c r="G29"/>
       <c r="H29"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D30"/>
       <c r="E30"/>
       <c r="F30"/>
       <c r="G30"/>
       <c r="H30"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D31"/>
       <c r="E31"/>
       <c r="F31"/>
       <c r="G31"/>
       <c r="H31"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="D32"/>
       <c r="E32"/>
       <c r="F32"/>
@@ -1202,8 +1746,6 @@
     <row r="49" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="50" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="51" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
